--- a/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
+++ b/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="20115" windowHeight="7995"/>
+    <workbookView xWindow="240" yWindow="75" windowWidth="20115" windowHeight="7995" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="CMYK" sheetId="1" r:id="rId1"/>
+    <sheet name="XYZ" sheetId="2" r:id="rId2"/>
+    <sheet name="Profile Options" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>CMYK_C</t>
   </si>
@@ -40,6 +40,60 @@
   </si>
   <si>
     <t>SrNo</t>
+  </si>
+  <si>
+    <t>Copyright Fujiflm Graphic Systems USA</t>
+  </si>
+  <si>
+    <t>Fuji</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Test Profiler WFC Service</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Creator</t>
+  </si>
+  <si>
+    <t>ProfileType</t>
+  </si>
+  <si>
+    <t>ProfileSize2</t>
+  </si>
+  <si>
+    <t>ProfileFormat4</t>
+  </si>
+  <si>
+    <t>SaveProfilerInfo1</t>
+  </si>
+  <si>
+    <t>GridA2B03</t>
+  </si>
+  <si>
+    <t>GridA2B23</t>
+  </si>
+  <si>
+    <t>GridB2A03</t>
+  </si>
+  <si>
+    <t>GridB2A13</t>
+  </si>
+  <si>
+    <t>GridB2A23</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -63508,9 +63562,119 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
+++ b/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>CMYK_C</t>
   </si>
@@ -95,12 +95,72 @@
   <si>
     <t>Value</t>
   </si>
+  <si>
+    <t>Source Profile</t>
+  </si>
+  <si>
+    <t>Device Link Profile</t>
+  </si>
+  <si>
+    <t>DeviceLink</t>
+  </si>
+  <si>
+    <t>ProfileSize</t>
+  </si>
+  <si>
+    <t>Rendering</t>
+  </si>
+  <si>
+    <t>PerceptualCompression2</t>
+  </si>
+  <si>
+    <t>PerceptualCompressionMergeFactor</t>
+  </si>
+  <si>
+    <t>DLType</t>
+  </si>
+  <si>
+    <t>DLExceptions</t>
+  </si>
+  <si>
+    <t>DLOptimizeExceptions</t>
+  </si>
+  <si>
+    <t>DLExceptionRange</t>
+  </si>
+  <si>
+    <t>DLOptimizeInkRange</t>
+  </si>
+  <si>
+    <t>7900/Xerox 1000 DLP Setting v1.0</t>
+  </si>
+  <si>
+    <t>BlackGeneration</t>
+  </si>
+  <si>
+    <t>GCR2Smooth</t>
+  </si>
+  <si>
+    <t>InkMax</t>
+  </si>
+  <si>
+    <t>79 79 77 95 BalanceCMY</t>
+  </si>
+  <si>
+    <t>InkTotal</t>
+  </si>
+  <si>
+    <t>BlackStart</t>
+  </si>
+  <si>
+    <t>BlackWidth</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +175,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,9 +203,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -63562,7 +63629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -63571,71 +63638,68 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -63643,7 +63707,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -63651,7 +63715,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -63659,7 +63723,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -63667,10 +63731,159 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="2">
+        <v>65536</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="2">
+        <v>524289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
+++ b/CPSyncService/ColorPathSyncTest/DataFiles/CMYK_XYZ Values.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>CMYK_C</t>
   </si>
@@ -42,34 +42,13 @@
     <t>SrNo</t>
   </si>
   <si>
-    <t>Copyright Fujiflm Graphic Systems USA</t>
-  </si>
-  <si>
-    <t>Fuji</t>
-  </si>
-  <si>
     <t>Printer</t>
   </si>
   <si>
     <t>Test Profiler WFC Service</t>
   </si>
   <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Creator</t>
-  </si>
-  <si>
     <t>ProfileType</t>
-  </si>
-  <si>
-    <t>ProfileSize2</t>
-  </si>
-  <si>
-    <t>ProfileFormat4</t>
-  </si>
-  <si>
-    <t>SaveProfilerInfo1</t>
   </si>
   <si>
     <t>GridA2B03</t>
@@ -155,6 +134,33 @@
   <si>
     <t>BlackWidth</t>
   </si>
+  <si>
+    <t>Optimize Profile</t>
+  </si>
+  <si>
+    <t>ProfileFormat</t>
+  </si>
+  <si>
+    <t>SaveProfilerInfo</t>
+  </si>
+  <si>
+    <t>OptimizeDeviceLink</t>
+  </si>
+  <si>
+    <t>DLBypassBlack</t>
+  </si>
+  <si>
+    <t>DLOptimizationLimit</t>
+  </si>
+  <si>
+    <t>Flags</t>
+  </si>
+  <si>
+    <t>Attributes0</t>
+  </si>
+  <si>
+    <t>Attributes1</t>
+  </si>
 </sst>
 </file>
 
@@ -191,7 +197,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -199,14 +205,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -63629,264 +63702,451 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="6" max="6" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="E1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="G8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5">
+        <v>65536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5">
+        <v>524289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E13" s="3">
+        <v>11</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="E14" s="3">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="3">
+        <v>13</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3">
+        <v>14</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>16</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>6</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
+      <c r="B25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>11</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="2">
-        <v>65536</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="2">
-        <v>524289</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="2">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33">
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A14:C14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
